--- a/data/trans_dic/IP16A11_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor</t>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -571,24 +572,24 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 33,49</t>
+          <t>6,58; 33,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 43,3</t>
+          <t>6,42; 41,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 31,95</t>
+          <t>10,53; 30,26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -621,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,69; 68,91</t>
+          <t>11,3; 70,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,62; 69,82</t>
+          <t>45,3; 70,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,6; 63,42</t>
+          <t>17,41; 63,74</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,72; 39,14</t>
+          <t>7,39; 38,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 20,14</t>
+          <t>3,55; 19,76</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,11; 66,97</t>
+          <t>17,86; 66,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,34; 67,68</t>
+          <t>11,3; 70,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,36; 61,07</t>
+          <t>20,57; 59,77</t>
         </is>
       </c>
     </row>
@@ -771,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,01; 53,23</t>
+          <t>12,35; 56,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 41,4</t>
+          <t>0,0; 39,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,98; 38,06</t>
+          <t>12,0; 41,18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -821,24 +822,24 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 57,44</t>
+          <t>6,86; 55,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,29</t>
+          <t>0,0; 21,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,12; 28,27</t>
+          <t>4,87; 30,06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>26,71; 55,84</t>
+          <t>27,35; 56,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>24,61; 53,86</t>
+          <t>25,58; 52,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,79; 51,56</t>
+          <t>29,86; 51,76</t>
         </is>
       </c>
     </row>
@@ -921,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,09; 55,78</t>
+          <t>5,88; 55,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,43</t>
+          <t>0,0; 45,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,92; 38,4</t>
+          <t>8,61; 38,93</t>
         </is>
       </c>
     </row>
@@ -971,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,31; 40,24</t>
+          <t>18,84; 40,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25,86; 39,1</t>
+          <t>26,39; 39,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24,16; 36,15</t>
+          <t>23,81; 36,94</t>
         </is>
       </c>
     </row>
@@ -1007,4 +1008,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>5407</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9980</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2000; 10146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1433; 9195</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5549; 15947</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>23680</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51595</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7204; 44640</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21817; 33882</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19484; 71328</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3741</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3741</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1356; 6990</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1372; 7635</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5014</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9318</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2236; 8359</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1251; 7810</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4853; 14103</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1084; 4951</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4403</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2396; 8225</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>527; 4242</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2973</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1036; 6400</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>12267</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>17184</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>29451</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>8147; 16756</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11345; 23471</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22136; 38374</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2121</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>477; 4465</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5314</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1706; 7715</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>57005</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>58569</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>115574</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>33793; 72844</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>48224; 71335</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>86219; 133730</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A11_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Provincia-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 33,39</t>
+          <t>6,43; 33,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 41,19</t>
+          <t>5,3; 40,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,53; 30,26</t>
+          <t>9,98; 32,71</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 70,03</t>
+          <t>11,49; 70,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,3; 70,35</t>
+          <t>46,02; 70,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 63,74</t>
+          <t>21,48; 63,58</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 38,09</t>
+          <t>7,0; 39,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 19,76</t>
+          <t>3,41; 19,7</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,86; 66,76</t>
+          <t>16,42; 66,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 70,53</t>
+          <t>11,85; 71,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,57; 59,77</t>
+          <t>21,47; 59,78</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,35; 56,41</t>
+          <t>11,63; 54,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,33</t>
+          <t>4,1; 42,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 41,18</t>
+          <t>10,22; 39,84</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,86; 55,24</t>
+          <t>7,11; 57,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,85</t>
+          <t>0,0; 21,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,87; 30,06</t>
+          <t>5,13; 28,45</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,35; 56,25</t>
+          <t>27,64; 56,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,58; 52,92</t>
+          <t>25,45; 54,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,86; 51,76</t>
+          <t>28,83; 51,85</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,88; 55,04</t>
+          <t>9,58; 56,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,4</t>
+          <t>0,0; 41,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,61; 38,93</t>
+          <t>8,05; 41,26</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,84; 40,62</t>
+          <t>19,91; 40,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,39; 39,04</t>
+          <t>26,16; 38,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23,81; 36,94</t>
+          <t>24,88; 37,03</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2000; 10146</t>
+          <t>1953; 10049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1433; 9195</t>
+          <t>1183; 9119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5549; 15947</t>
+          <t>5259; 17241</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7204; 44640</t>
+          <t>7322; 44694</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21817; 33882</t>
+          <t>22167; 33807</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19484; 71328</t>
+          <t>24035; 71150</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1356; 6990</t>
+          <t>1285; 7203</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1372; 7635</t>
+          <t>1318; 7611</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2236; 8359</t>
+          <t>2055; 8305</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1251; 7810</t>
+          <t>1312; 7903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4853; 14103</t>
+          <t>5065; 14103</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1084; 4951</t>
+          <t>1021; 4812</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4403</t>
+          <t>459; 4810</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2396; 8225</t>
+          <t>2040; 7958</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>527; 4242</t>
+          <t>546; 4426</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2973</t>
+          <t>0; 2951</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1036; 6400</t>
+          <t>1093; 6056</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8147; 16756</t>
+          <t>8234; 16796</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11345; 23471</t>
+          <t>11290; 24160</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22136; 38374</t>
+          <t>21374; 38443</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>477; 4465</t>
+          <t>777; 4563</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 5314</t>
+          <t>0; 4845</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1706; 7715</t>
+          <t>1596; 8178</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>33793; 72844</t>
+          <t>35717; 73114</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>48224; 71335</t>
+          <t>47794; 69961</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>86219; 133730</t>
+          <t>90094; 134078</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A11_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP16A11_2023-Provincia-trans_dic.xlsx
@@ -490,18 +490,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 33,07</t>
+          <t>6,38; 39,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 40,85</t>
+          <t>12,1; 42,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,98; 32,71</t>
+          <t>12,65; 35,28</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 70,12</t>
+          <t>43,98; 70,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,02; 70,19</t>
+          <t>42,45; 72,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,48; 63,58</t>
+          <t>48,32; 67,1</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 39,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,93; 39,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 19,7</t>
+          <t>3,71; 20,69</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,42; 66,33</t>
+          <t>11,22; 68,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 71,37</t>
+          <t>15,03; 61,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,47; 59,78</t>
+          <t>21,95; 61,65</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,63; 54,82</t>
+          <t>4,94; 45,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 42,96</t>
+          <t>11,59; 54,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 39,84</t>
+          <t>12,36; 42,43</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,11; 57,64</t>
+          <t>0,0; 25,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,69</t>
+          <t>7,93; 57,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,13; 28,45</t>
+          <t>5,65; 30,46</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,64; 56,39</t>
+          <t>23,54; 52,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,45; 54,47</t>
+          <t>27,64; 56,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,83; 51,85</t>
+          <t>28,81; 51,06</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,58; 56,24</t>
+          <t>0,0; 46,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,39</t>
+          <t>8,62; 57,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,05; 41,26</t>
+          <t>8,05; 39,89</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19,91; 40,77</t>
+          <t>25,79; 38,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26,16; 38,29</t>
+          <t>32,78; 45,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24,88; 37,03</t>
+          <t>30,14; 39,27</t>
         </is>
       </c>
     </row>
@@ -1029,18 +1029,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
+          <t>Menores que consumieron medicamentos para el dolor (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>8713</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1953; 10049</t>
+          <t>1229; 7678</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1183; 9119</t>
+          <t>2516; 8941</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5259; 17241</t>
+          <t>5070; 14139</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23680</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51595</t>
+          <t>47871</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7322; 44694</t>
+          <t>18766; 29870</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22167; 33807</t>
+          <t>16781; 28851</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24035; 71150</t>
+          <t>39722; 55160</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3646</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1285; 7203</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1388; 6868</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1318; 7611</t>
+          <t>1304; 7279</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>8666</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2055; 8305</t>
+          <t>1168; 7169</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1312; 7903</t>
+          <t>1837; 7471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5065; 14103</t>
+          <t>4970; 13956</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4876</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1021; 4812</t>
+          <t>508; 4665</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>459; 4810</t>
+          <t>1045; 4869</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2040; 7958</t>
+          <t>2382; 8181</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>827</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2837</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>546; 4426</t>
+          <t>0; 2920</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2951</t>
+          <t>607; 4392</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1093; 6056</t>
+          <t>1080; 5817</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17184</t>
+          <t>12632</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>28510</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8234; 16796</t>
+          <t>9895; 22136</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11290; 24160</t>
+          <t>8367; 17188</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21374; 38443</t>
+          <t>20830; 36915</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3937</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>777; 4563</t>
+          <t>0; 5398</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4845</t>
+          <t>658; 4417</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1596; 8178</t>
+          <t>1557; 7716</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>57005</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>35717; 73114</t>
+          <t>42683; 63754</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>47794; 69961</t>
+          <t>47419; 66158</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90094; 134078</t>
+          <t>93456; 121778</t>
         </is>
       </c>
     </row>
